--- a/autoIt/ExportFiles/StockTransferHomeExcel.xlsx
+++ b/autoIt/ExportFiles/StockTransferHomeExcel.xlsx
@@ -23,7 +23,7 @@
     <t xml:space="preserve">InvTag2 Name = wh6</t>
   </si>
   <si>
-    <t xml:space="preserve">[As on date 18/05/2026]</t>
+    <t xml:space="preserve">[As on date 23/05/2026]</t>
   </si>
   <si>
     <t xml:space="preserve">DocNo</t>

--- a/autoIt/ExportFiles/StockTransferHomeExcel.xlsx
+++ b/autoIt/ExportFiles/StockTransferHomeExcel.xlsx
@@ -23,7 +23,7 @@
     <t xml:space="preserve">InvTag2 Name = wh6</t>
   </si>
   <si>
-    <t xml:space="preserve">[As on date 04/06/2026]</t>
+    <t xml:space="preserve">[As on date 05/06/2026]</t>
   </si>
   <si>
     <t xml:space="preserve">DocNo</t>

--- a/autoIt/ExportFiles/StockTransferHomeExcel.xlsx
+++ b/autoIt/ExportFiles/StockTransferHomeExcel.xlsx
@@ -23,7 +23,7 @@
     <t xml:space="preserve">InvTag2 Name = wh6</t>
   </si>
   <si>
-    <t xml:space="preserve">[As on date 05/06/2026]</t>
+    <t xml:space="preserve">[As on date 22/06/2026]</t>
   </si>
   <si>
     <t xml:space="preserve">DocNo</t>
